--- a/outputs/evaluation/architecture/CF_M08_arch_eval_llm_report.xlsx
+++ b/outputs/evaluation/architecture/CF_M08_arch_eval_llm_report.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L14"/>
+  <dimension ref="A1:L15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -523,70 +523,70 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0.0612</v>
+        <v>0.0643</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AU_03</t>
+          <t>AU_15</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Traefik</t>
+          <t>Analytics Service</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Service</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Reverse proxy and load balancer tool.</t>
+          <t>External service for tracking and analyzing site traffic.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>41, 43</t>
+          <t>42</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>AU_02</t>
+          <t>AU_04</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
-          <t>CF_M08_AU03</t>
+          <t>CF_M08_AU17</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Traffic</t>
+          <t>Google Analytics</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Security Service (Traefik)</t>
+          <t>Implement Google Analytics to track and analyze site traffic</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0.1492</v>
+        <v>0.7045</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AU_16</t>
+          <t>AU_17</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Analytics Service</t>
+          <t>Error Tracking Service</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -596,7 +596,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>External service for tracking and analyzing site traffic.</t>
+          <t>External service for monitoring and managing application errors.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -604,32 +604,36 @@
           <t>42</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>AU_04</t>
+        </is>
+      </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>CF_M08_AU17</t>
+          <t>CF_M08_AU18</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Google Analytics</t>
+          <t>Error monitoring</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Implement Google Analytics to track and analyze site traffic</t>
+          <t>Error monitoring</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0.7081</v>
+        <v>0.3288</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AU_21</t>
+          <t>AU_20</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -644,17 +648,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Email and marketing communication platform.</t>
+          <t>Email marketing and communication platform used for the Email Service.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>42, 73</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>AU_20</t>
+          <t>AU_19</t>
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
@@ -675,169 +679,165 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0.0576</v>
+        <v>0.0602</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AU_22</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Server Component</t>
-        </is>
-      </c>
+          <t>AU_23</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Component</t>
+          <t>Connector</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Next.js component rendered on the server.</t>
+          <t>The User interacts with the Security Service (Traefik).</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>44, 78</t>
+          <t>41, 43</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>AU_04</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr"/>
+          <t>AU_01, AU_02</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>user, security service</t>
+        </is>
+      </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>CF_M08_AD03</t>
+          <t>CF_M08_AU02</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Component-based</t>
+          <t>Security Service</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>The Component-Based pattern focuses on building the user interface by creating independent and reusable components</t>
+          <t>It works as a reverse proxy and load balancer. • Manages the routing of HTTP and HTTPS requests towards the Next.js application (System Service). • Exposes ports 80 (HTTP) and 443 (HTTPS) to the outside world and redirects traffic to internal services according to defined rules</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0.5143</v>
+        <v>0.5196</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AU_23</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Client Component</t>
-        </is>
-      </c>
+          <t>AU_24</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Component</t>
+          <t>Connector</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Next.js component rendered on the client.</t>
+          <t>The Security Service (Traefik) routes traffic to the System Service (Next.js).</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>44, 82</t>
+          <t>41, 43</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>AU_04</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr"/>
+          <t>AU_02, AU_04</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>security service, system service</t>
+        </is>
+      </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>CF_M08_AD03</t>
+          <t>CF_M08_AU02</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Component-based</t>
+          <t>Security Service</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>The Component-Based pattern focuses on building the user interface by creating independent and reusable components</t>
+          <t>It works as a reverse proxy and load balancer. • Manages the routing of HTTP and HTTPS requests towards the Next.js application (System Service). • Exposes ports 80 (HTTP) and 443 (HTTPS) to the outside world and redirects traffic to internal services according to defined rules</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0.4458</v>
+        <v>0.4728</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AU_24</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Server Action</t>
-        </is>
-      </c>
+          <t>AU_25</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Component</t>
+          <t>Connector</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Mechanism for client components to execute server-side logic.</t>
+          <t>The System Service (Next.js) communicates with the Data Service (PostgreSQL) using Prisma.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>46, 84</t>
+          <t>41, 42</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>AU_04</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr"/>
+          <t>AU_04, AU_07</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>system service, data service</t>
+        </is>
+      </c>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
-          <t>CF_M08_AD04</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>Observer</t>
-        </is>
-      </c>
+          <t>CF_M08_AU24</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
-          <t>The Observer pattern establishes a one-to-many relationship between objects, where an object known as the subject maintains a list of other objects called observers. These observers subscribe to the subject to receive notifications of changes in their status. When the state of the subject changes, it automatically notifies all its observers, allowing them to react appropriately</t>
+          <t>• It communicates with the PostgreSQL database service</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0.3876</v>
+        <v>0.5987</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AU_26</t>
+          <t>AU_28</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -848,48 +848,48 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>User to Security Service connection.</t>
+          <t>The System Service (Next.js) interacts with the Payment Service (Stripe).</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>42</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>AU_01, AU_02</t>
+          <t>AU_04, AU_13</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>user, security service</t>
+          <t>system service, payment service</t>
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
-          <t>CF_M08_AU02</t>
+          <t>CF_M08_AU04</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Security Service</t>
+          <t>System Service</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>It works as a reverse proxy and load balancer. • Manages the routing of HTTP and HTTPS requests towards the Next.js application (System Service). • Exposes ports 80 (HTTP) and 443 (HTTPS) to the outside world and redirects traffic to internal services according to defined rules</t>
+          <t>It serves the web application using React. • It communicates with the PostgreSQL database service (Data Service) using Prisma as ORM7 (Object-Relational Mapping). • It depends on Traefik to receive and manage HTTP/HTTPS traffic. • Interacts with various external services for specific functionalities</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0.6226</v>
+        <v>0.4509</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AU_27</t>
+          <t>AU_29</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -900,48 +900,48 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Security Service to System Service connection.</t>
+          <t>The System Service (Next.js) interacts with the Analytics Service (Google Analytics).</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>42</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>AU_02, AU_04</t>
+          <t>AU_04, AU_15</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>security service, system service</t>
+          <t>system service, analytics service</t>
         </is>
       </c>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
-          <t>CF_M08_AU02</t>
+          <t>CF_M08_AU17</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Security Service</t>
+          <t>Google Analytics</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>It works as a reverse proxy and load balancer. • Manages the routing of HTTP and HTTPS requests towards the Next.js application (System Service). • Exposes ports 80 (HTTP) and 443 (HTTPS) to the outside world and redirects traffic to internal services according to defined rules</t>
+          <t>Implement Google Analytics to track and analyze site traffic</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0.6706</v>
+        <v>0.6371</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AU_28</t>
+          <t>AU_30</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
@@ -952,7 +952,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>System Service to Data Service connection.</t>
+          <t>The System Service (Next.js) interacts with the Error Tracking Service (Sentry).</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -962,95 +962,95 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>AU_04, AU_06</t>
+          <t>AU_04, AU_17</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>system service, data service</t>
+          <t>system service, error tracking service</t>
         </is>
       </c>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
-          <t>CF_M08_AU07</t>
+          <t>CF_M08_AU04</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Data Service</t>
+          <t>System Service</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Data Service: • Provides the relational database to store application data. • Communicates directly with Prisma to manage database queries</t>
+          <t>It serves the web application using React. • It communicates with the PostgreSQL database service (Data Service) using Prisma as ORM7 (Object-Relational Mapping). • It depends on Traefik to receive and manage HTTP/HTTPS traffic. • Interacts with various external services for specific functionalities</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0.6829</v>
+        <v>0.4196</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>P_02</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Reverse Proxy</t>
-        </is>
-      </c>
+          <t>AU_32</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Design Pattern</t>
+          <t>Connector</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Traefik acts as an intermediary for client requests, redirecting incoming traffic to the appropriate internal services.</t>
+          <t>The User interacts with the System Service (Next.js) via client components.</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>41, 43</t>
+          <t>44</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>P_01</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr"/>
+          <t>AU_01, AU_04</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>user, system service</t>
+        </is>
+      </c>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
-          <t>CF_M08_AU14</t>
+          <t>CF_M08_AU04</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Payment processing</t>
+          <t>System Service</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Payment processing</t>
+          <t>It serves the web application using React. • It communicates with the PostgreSQL database service (Data Service) using Prisma as ORM7 (Object-Relational Mapping). • It depends on Traefik to receive and manage HTTP/HTTPS traffic. • Interacts with various external services for specific functionalities</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0.0669</v>
+        <v>0.3259</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>P_03</t>
+          <t>P_02</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Load Balancer</t>
+          <t>Reverse Proxy</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1060,7 +1060,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Traefik distributes incoming traffic across multiple service instances to improve availability and responsiveness.</t>
+          <t>Traefik acts as an intermediary for client requests, redirecting incoming traffic to the appropriate internal services.</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1077,32 +1077,32 @@
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
-          <t>CF_M08_AU22</t>
+          <t>CF_M08_AU14</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Docker</t>
+          <t>Payment processing</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Each of these services is contained in a Docker container</t>
+          <t>Payment processing</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0.021</v>
+        <v>0.0675</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>P_07</t>
+          <t>P_03</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ORM (Object-Relational Mapping)</t>
+          <t>Load Balancer</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1112,34 +1112,86 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Technique used to convert data between the object-oriented programming system and the relational database, implemented via Prisma.</t>
+          <t>Traefik distributes incoming traffic across multiple service instances to improve availability and responsiveness.</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>42, 50</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr"/>
+          <t>41, 43</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>P_01</t>
+        </is>
+      </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
+          <t>CF_M08_AU22</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Docker</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Each of these services is contained in a Docker container</t>
+        </is>
+      </c>
+      <c r="L14" t="n">
+        <v>0.0226</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>P_07</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>ORM (Object-Relational Mapping)</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Design Pattern</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Technique used to convert data between the object-oriented programming system and the relational database, implemented via Prisma.</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>42, 50</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
           <t>CF_M08_AD02</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t>ORM</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t>(footnote) It is a programming technique to convert data between the type system used in an object-oriented programming language and the use of a relational database as a persistence engine (Atencio 2016).</t>
         </is>
       </c>
-      <c r="L14" t="n">
-        <v>0.3274</v>
+      <c r="L15" t="n">
+        <v>0.3491</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/evaluation/architecture/CF_M08_arch_eval_llm_report.xlsx
+++ b/outputs/evaluation/architecture/CF_M08_arch_eval_llm_report.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L15"/>
+  <dimension ref="A1:L8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -496,7 +496,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Individual or entity (donor or company) that interacts with the system.</t>
+          <t>Any individual or entity that interacts with the system, including donors and companies.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -509,7 +509,7 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
-          <t>CF_M08_AD04</t>
+          <t>CF_M08_P04</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -523,180 +523,180 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0.0643</v>
+        <v>0.0639</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AU_15</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Analytics Service</t>
-        </is>
-      </c>
+          <t>AU_24</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Connector</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>External service for tracking and analyzing site traffic.</t>
+          <t>The User interacts with the Security Service (Traefik) to access the system.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>41, 43</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>AU_04</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr"/>
+          <t>AU_01, AU_02</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>user, security service</t>
+        </is>
+      </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
-          <t>CF_M08_AU17</t>
+          <t>CF_M08_AU02</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Google Analytics</t>
+          <t>Security Service</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Implement Google Analytics to track and analyze site traffic</t>
+          <t>It works as a reverse proxy and load balancer. • Manages the routing of HTTP and HTTPS requests towards the Next.js application (System Service). • Exposes ports 80 (HTTP) and 443 (HTTPS) to the outside world and redirects traffic to internal services according to defined rules</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0.7045</v>
+        <v>0.4305</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AU_17</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Error Tracking Service</t>
-        </is>
-      </c>
+          <t>AU_25</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Connector</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>External service for monitoring and managing application errors.</t>
+          <t>The Security Service (Traefik) routes HTTP/HTTPS traffic to the System Service.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>41, 43</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>AU_04</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr"/>
+          <t>AU_02, AU_04</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>security service, system service</t>
+        </is>
+      </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>CF_M08_AU18</t>
+          <t>CF_M08_AU02</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Error monitoring</t>
+          <t>Security Service</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Error monitoring</t>
+          <t>It works as a reverse proxy and load balancer. • Manages the routing of HTTP and HTTPS requests towards the Next.js application (System Service). • Exposes ports 80 (HTTP) and 443 (HTTPS) to the outside world and redirects traffic to internal services according to defined rules</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0.3288</v>
+        <v>0.4206</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AU_20</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Brevo</t>
-        </is>
-      </c>
+          <t>AU_26</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Connector</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Email marketing and communication platform used for the Email Service.</t>
+          <t>The System Service communicates with the Data Service (PostgreSQL) using Prisma.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>42, 73</t>
+          <t>42</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>AU_19</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr"/>
+          <t>AU_04, AU_07</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>system service, data service</t>
+        </is>
+      </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>CF_M08_AU21</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Briefly</t>
-        </is>
-      </c>
+          <t>CF_M08_AU24</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Connects to Brevo to create, send and schedule emails.</t>
+          <t>• It communicates with the PostgreSQL database service</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0.0602</v>
+        <v>0.6284999999999999</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AU_23</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr"/>
+          <t>P_02</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Reverse Proxy</t>
+        </is>
+      </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Connector</t>
+          <t>Design Pattern</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>The User interacts with the Security Service (Traefik).</t>
+          <t>Traefik acts as an intermediary for client requests, redirecting incoming traffic to the appropriate internal services.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -706,49 +706,49 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>AU_01, AU_02</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>user, security service</t>
-        </is>
-      </c>
+          <t>P_01</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>CF_M08_AU02</t>
+          <t>CF_M08_AU14</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Security Service</t>
+          <t>Payment processing</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>It works as a reverse proxy and load balancer. • Manages the routing of HTTP and HTTPS requests towards the Next.js application (System Service). • Exposes ports 80 (HTTP) and 443 (HTTPS) to the outside world and redirects traffic to internal services according to defined rules</t>
+          <t>Payment processing</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0.5196</v>
+        <v>0.0598</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AU_24</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr"/>
+          <t>P_03</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Load Balancer</t>
+        </is>
+      </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Connector</t>
+          <t>Design Pattern</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>The Security Service (Traefik) routes traffic to the System Service (Next.js).</t>
+          <t>Traefik distributes incoming traffic across multiple instances of services to improve availability and responsiveness.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -758,439 +758,75 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>AU_02, AU_04</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>security service, system service</t>
-        </is>
-      </c>
+          <t>P_01</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>CF_M08_AU02</t>
+          <t>CF_M08_AU22</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Security Service</t>
+          <t>Docker</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>It works as a reverse proxy and load balancer. • Manages the routing of HTTP and HTTPS requests towards the Next.js application (System Service). • Exposes ports 80 (HTTP) and 443 (HTTPS) to the outside world and redirects traffic to internal services according to defined rules</t>
+          <t>Each of these services is contained in a Docker container</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0.4728</v>
+        <v>0.0242</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AU_25</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr"/>
+          <t>P_07</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>ORM (Object-Relational Mapping)</t>
+        </is>
+      </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Connector</t>
+          <t>Design Pattern</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>The System Service (Next.js) communicates with the Data Service (PostgreSQL) using Prisma.</t>
+          <t>Technique used to convert data between the object-oriented programming system and the relational database, implemented via Prisma.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>41, 42</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>AU_04, AU_07</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>system service, data service</t>
-        </is>
-      </c>
+          <t>42, 50</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
-          <t>CF_M08_AU24</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr"/>
+          <t>CF_M08_P02</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>ORM</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>• It communicates with the PostgreSQL database service</t>
+          <t>(footnote) It is a programming technique to convert data between the type system used in an object-oriented programming language and the use of a relational database as a persistence engine (Atencio 2016).</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0.5987</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>AU_28</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Connector</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>The System Service (Next.js) interacts with the Payment Service (Stripe).</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>AU_04, AU_13</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>system service, payment service</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>CF_M08_AU04</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>System Service</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>It serves the web application using React. • It communicates with the PostgreSQL database service (Data Service) using Prisma as ORM7 (Object-Relational Mapping). • It depends on Traefik to receive and manage HTTP/HTTPS traffic. • Interacts with various external services for specific functionalities</t>
-        </is>
-      </c>
-      <c r="L9" t="n">
-        <v>0.4509</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>AU_29</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Connector</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>The System Service (Next.js) interacts with the Analytics Service (Google Analytics).</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>AU_04, AU_15</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>system service, analytics service</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>CF_M08_AU17</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>Google Analytics</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>Implement Google Analytics to track and analyze site traffic</t>
-        </is>
-      </c>
-      <c r="L10" t="n">
-        <v>0.6371</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>AU_30</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Connector</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>The System Service (Next.js) interacts with the Error Tracking Service (Sentry).</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>AU_04, AU_17</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>system service, error tracking service</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>CF_M08_AU04</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>System Service</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>It serves the web application using React. • It communicates with the PostgreSQL database service (Data Service) using Prisma as ORM7 (Object-Relational Mapping). • It depends on Traefik to receive and manage HTTP/HTTPS traffic. • Interacts with various external services for specific functionalities</t>
-        </is>
-      </c>
-      <c r="L11" t="n">
-        <v>0.4196</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>AU_32</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Connector</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>The User interacts with the System Service (Next.js) via client components.</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>AU_01, AU_04</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>user, system service</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>CF_M08_AU04</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>System Service</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>It serves the web application using React. • It communicates with the PostgreSQL database service (Data Service) using Prisma as ORM7 (Object-Relational Mapping). • It depends on Traefik to receive and manage HTTP/HTTPS traffic. • Interacts with various external services for specific functionalities</t>
-        </is>
-      </c>
-      <c r="L12" t="n">
-        <v>0.3259</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>P_02</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Reverse Proxy</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Design Pattern</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Traefik acts as an intermediary for client requests, redirecting incoming traffic to the appropriate internal services.</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>41, 43</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>P_01</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>CF_M08_AU14</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>Payment processing</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>Payment processing</t>
-        </is>
-      </c>
-      <c r="L13" t="n">
-        <v>0.0675</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>P_03</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Load Balancer</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Design Pattern</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Traefik distributes incoming traffic across multiple service instances to improve availability and responsiveness.</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>41, 43</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>P_01</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>CF_M08_AU22</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>Docker</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>Each of these services is contained in a Docker container</t>
-        </is>
-      </c>
-      <c r="L14" t="n">
-        <v>0.0226</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>P_07</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>ORM (Object-Relational Mapping)</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Design Pattern</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Technique used to convert data between the object-oriented programming system and the relational database, implemented via Prisma.</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>42, 50</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>CF_M08_AD02</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>ORM</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>(footnote) It is a programming technique to convert data between the type system used in an object-oriented programming language and the use of a relational database as a persistence engine (Atencio 2016).</t>
-        </is>
-      </c>
-      <c r="L15" t="n">
         <v>0.3491</v>
       </c>
     </row>

--- a/outputs/evaluation/architecture/CF_M08_arch_eval_llm_report.xlsx
+++ b/outputs/evaluation/architecture/CF_M08_arch_eval_llm_report.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L8"/>
+  <dimension ref="A1:L7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -481,49 +481,53 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>AU_20</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Gestiona el enrutamiento de solicitudes HTTP y HTTPS hacia la aplicación Next.js.</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t>AU_01</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>User</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Any individual or entity that interacts with the system, including donors and companies.</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
-          <t>CF_M08_P04</t>
+          <t>CF_M08_AU23</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Observer</t>
+          <t>HTTPS</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>The Observer pattern establishes a one-to-many relationship between objects, where an object known as the subject maintains a list of other objects called observers. These observers subscribe to the subject to receive notifications of changes in their status. When the state of the subject changes, it automatically notifies all its observers, allowing them to react appropriately</t>
+          <t>HTTPS, which is the standard for secure communications on the web</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0.0639</v>
+        <v>0.894</v>
       </c>
     </row>
     <row r="3">
@@ -532,50 +536,46 @@
           <t>AU_24</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Connector</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>The User interacts with the Security Service (Traefik) to access the system.</t>
+          <t>Un usuario es todo individuo o entidad que interactúa con el sistema, puede ser tanto un donante como una empresa.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>41, 43</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>AU_01, AU_02</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>user, security service</t>
-        </is>
-      </c>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
-          <t>CF_M08_AU02</t>
+          <t>CF_M08_P06</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Security Service</t>
+          <t>Client-Server</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>It works as a reverse proxy and load balancer. • Manages the routing of HTTP and HTTPS requests towards the Next.js application (System Service). • Exposes ports 80 (HTTP) and 443 (HTTPS) to the outside world and redirects traffic to internal services according to defined rules</t>
+          <t xml:space="preserve"> The Revivack application mainly uses Next.js for system development, which allows to separate the components between client and server rendering</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0.4305</v>
+        <v>0.714</v>
       </c>
     </row>
     <row r="4">
@@ -592,42 +592,42 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>The Security Service (Traefik) routes HTTP/HTTPS traffic to the System Service.</t>
+          <t>Traefik gestiona el enrutamiento de solicitudes HTTP y HTTPS hacia la aplicación Next.js (System Service).</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>41, 43</t>
+          <t>41</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>AU_02, AU_04</t>
+          <t>AU_02, AU_03</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>security service, system service</t>
+          <t>traefik, system service</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>CF_M08_AU02</t>
+          <t>CF_M08_AU03</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Security Service</t>
+          <t>Traefik</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>It works as a reverse proxy and load balancer. • Manages the routing of HTTP and HTTPS requests towards the Next.js application (System Service). • Exposes ports 80 (HTTP) and 443 (HTTPS) to the outside world and redirects traffic to internal services according to defined rules</t>
+          <t>Security Service (Traefik)</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0.4206</v>
+        <v>0.7524</v>
       </c>
     </row>
     <row r="5">
@@ -644,7 +644,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>The System Service communicates with the Data Service (PostgreSQL) using Prisma.</t>
+          <t>System Service (Next.js) se comunica con el servicio de base de datos PostgreSQL (Data Service) utilizando Prisma como ORM.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -654,7 +654,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>AU_04, AU_07</t>
+          <t>AU_03, AU_05</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -675,159 +675,107 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0.6284999999999999</v>
+        <v>0.8296</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>P_02</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Reverse Proxy</t>
-        </is>
-      </c>
+          <t>AU_28</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Design Pattern</t>
+          <t>Connector</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Traefik acts as an intermediary for client requests, redirecting incoming traffic to the appropriate internal services.</t>
+          <t>Data Service (PostgreSQL) se comunica directamente con Prisma para gestionar las consultas de la base de datos.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>41, 43</t>
+          <t>42</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>P_01</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr"/>
+          <t>AU_05, AU_07</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>data service, prisma</t>
+        </is>
+      </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>CF_M08_AU14</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>Payment processing</t>
-        </is>
-      </c>
+          <t>CF_M08_AU24</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Payment processing</t>
+          <t>• It communicates with the PostgreSQL database service</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0.0598</v>
+        <v>0.8529</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>P_03</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Load Balancer</t>
-        </is>
-      </c>
+          <t>AU_29</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Design Pattern</t>
+          <t>Connector</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Traefik distributes incoming traffic across multiple instances of services to improve availability and responsiveness.</t>
+          <t>Un usuario es todo individuo o entidad que interactúa con el sistema</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>41, 43</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>P_01</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr"/>
+          <t>AU_24, AU_03</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>user, system service</t>
+        </is>
+      </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>CF_M08_AU22</t>
+          <t>CF_M08_P06</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Docker</t>
+          <t>Client-Server</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Each of these services is contained in a Docker container</t>
+          <t xml:space="preserve"> The Revivack application mainly uses Next.js for system development, which allows to separate the components between client and server rendering</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0.0242</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>P_07</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>ORM (Object-Relational Mapping)</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Design Pattern</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Technique used to convert data between the object-oriented programming system and the relational database, implemented via Prisma.</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>42, 50</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>CF_M08_P02</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>ORM</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>(footnote) It is a programming technique to convert data between the type system used in an object-oriented programming language and the use of a relational database as a persistence engine (Atencio 2016).</t>
-        </is>
-      </c>
-      <c r="L8" t="n">
-        <v>0.3491</v>
+        <v>0.6612</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/evaluation/architecture/CF_M08_arch_eval_llm_report.xlsx
+++ b/outputs/evaluation/architecture/CF_M08_arch_eval_llm_report.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L7"/>
+  <dimension ref="A1:L8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -481,153 +481,153 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AU_20</t>
+          <t>AU_01</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>HTTP</t>
+          <t>User</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Gestiona el enrutamiento de solicitudes HTTP y HTTPS hacia la aplicación Next.js.</t>
+          <t>Un usuario es todo individuo o entidad que interactúa con el sistema, puede ser tanto un donante como una empresa.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>AU_01</t>
-        </is>
-      </c>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
-          <t>CF_M08_AU23</t>
+          <t>CF_M08_P06</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>HTTPS</t>
+          <t>Client-Server</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>HTTPS, which is the standard for secure communications on the web</t>
+          <t xml:space="preserve"> The Revivack application mainly uses Next.js for system development, which allows to separate the components between client and server rendering</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0.894</v>
+        <v>0.714</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AU_24</t>
+          <t>AU_20</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>User</t>
+          <t>HTTP</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Un usuario es todo individuo o entidad que interactúa con el sistema, puede ser tanto un donante como una empresa.</t>
+          <t>Gestiona el enrutamiento de solicitudes HTTP y HTTPS hacia la aplicación Next.js.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr"/>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>AU_02</t>
+        </is>
+      </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
-          <t>CF_M08_P06</t>
+          <t>CF_M08_AU23</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Client-Server</t>
+          <t>HTTPS</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t xml:space="preserve"> The Revivack application mainly uses Next.js for system development, which allows to separate the components between client and server rendering</t>
+          <t>HTTPS, which is the standard for secure communications on the web</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0.714</v>
+        <v>0.894</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AU_25</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr"/>
+          <t>AU_23</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>TypeScript</t>
+        </is>
+      </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Connector</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Traefik gestiona el enrutamiento de solicitudes HTTP y HTTPS hacia la aplicación Next.js (System Service).</t>
+          <t>Cabe destacar que para desarrollar el sistema se ha empleado el lenguaje TypeScript.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>73</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>AU_02, AU_03</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>traefik, system service</t>
-        </is>
-      </c>
+          <t>AU_04</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>CF_M08_AU03</t>
+          <t>CF_M08_AU05</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Traefik</t>
+          <t>Next.js</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Security Service (Traefik)</t>
+          <t>System Service (Next.js)</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0.7524</v>
+        <v>0.6879999999999999</v>
       </c>
     </row>
     <row r="5">
@@ -644,44 +644,48 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>System Service (Next.js) se comunica con el servicio de base de datos PostgreSQL (Data Service) utilizando Prisma como ORM.</t>
+          <t>Gestiona el enrutamiento de solicitudes HTTP y HTTPS hacia la aplicación Next.js (System Service).</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>41</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>AU_03, AU_05</t>
+          <t>AU_02, AU_04</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>system service, data service</t>
+          <t>security service, system service</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>CF_M08_AU24</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr"/>
+          <t>CF_M08_AU05</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Next.js</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>• It communicates with the PostgreSQL database service</t>
+          <t>System Service (Next.js)</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0.8296</v>
+        <v>0.7444</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AU_28</t>
+          <t>AU_27</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -692,7 +696,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Data Service (PostgreSQL) se comunica directamente con Prisma para gestionar las consultas de la base de datos.</t>
+          <t>Se comunica con el servicio de base de datos PostgreSQL (Data Service) utilizando Prisma como ORM.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -702,12 +706,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>AU_05, AU_07</t>
+          <t>AU_04, AU_06</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>data service, prisma</t>
+          <t>system service, data service</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
@@ -723,7 +727,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0.8529</v>
+        <v>0.8608</v>
       </c>
     </row>
     <row r="7">
@@ -740,42 +744,90 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Un usuario es todo individuo o entidad que interactúa con el sistema</t>
+          <t>Se comunica directamente con Prisma para gestionar las consultas de la base de datos.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>42</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>AU_24, AU_03</t>
+          <t>AU_06, AU_25</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>user, system service</t>
+          <t>data service, prisma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
+          <t>CF_M08_AU24</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>• It communicates with the PostgreSQL database service</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>0.7562</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>AU_30</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Al interactuar con un componente de cliente, este puede acceder al servidor mediante el uso de las server actions.</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>AU_04, AU_04</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>system service, system service</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
           <t>CF_M08_P06</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>Client-Server</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t xml:space="preserve"> The Revivack application mainly uses Next.js for system development, which allows to separate the components between client and server rendering</t>
         </is>
       </c>
-      <c r="L7" t="n">
-        <v>0.6612</v>
+      <c r="L8" t="n">
+        <v>0.8107</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/evaluation/architecture/CF_M08_arch_eval_llm_report.xlsx
+++ b/outputs/evaluation/architecture/CF_M08_arch_eval_llm_report.xlsx
@@ -529,12 +529,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AU_20</t>
+          <t>AU_23</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>HTTP</t>
+          <t>TypeScript</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -544,96 +544,96 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Gestiona el enrutamiento de solicitudes HTTP y HTTPS hacia la aplicación Next.js.</t>
+          <t>Cabe destacar que para desarrollar el sistema se ha empleado el lenguaje TypeScript.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>73</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>AU_02</t>
+          <t>AU_04</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
-          <t>CF_M08_AU23</t>
+          <t>CF_M08_AU05</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>HTTPS</t>
+          <t>Next.js</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>HTTPS, which is the standard for secure communications on the web</t>
+          <t>System Service (Next.js)</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0.894</v>
+        <v>0.6879999999999999</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AU_23</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>TypeScript</t>
-        </is>
-      </c>
+          <t>AU_24</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Connector</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Cabe destacar que para desarrollar el sistema se ha empleado el lenguaje TypeScript.</t>
+          <t>Security Service (Traefik) [...] Gestiona el enrutamiento de solicitudes HTTP y HTTPS hacia la aplicación Next.js (System Service).</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>41</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>AU_04</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr"/>
+          <t>AU_02, AU_04</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>security service, system service</t>
+        </is>
+      </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>CF_M08_AU05</t>
+          <t>CF_M08_AU23</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Next.js</t>
+          <t>HTTPS</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>System Service (Next.js)</t>
+          <t>HTTPS, which is the standard for secure communications on the web</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.7383</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AU_26</t>
+          <t>AU_25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -644,48 +644,44 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Gestiona el enrutamiento de solicitudes HTTP y HTTPS hacia la aplicación Next.js (System Service).</t>
+          <t>System Service (Next.js) [...] Se comunica con el servicio de base de datos PostgreSQL (Data Service) utilizando Prisma como ORM.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>42</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>AU_02, AU_04</t>
+          <t>AU_04, AU_06</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>security service, system service</t>
+          <t>system service, data service</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>CF_M08_AU05</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Next.js</t>
-        </is>
-      </c>
+          <t>CF_M08_AU24</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
-          <t>System Service (Next.js)</t>
+          <t>• It communicates with the PostgreSQL database service</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0.7444</v>
+        <v>0.8399</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AU_27</t>
+          <t>AU_26</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -696,7 +692,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Se comunica con el servicio de base de datos PostgreSQL (Data Service) utilizando Prisma como ORM.</t>
+          <t>System Service (Next.js) [...] Interactúa con varios servicios externos para funcionalidades específicas: Autenticación: Utiliza Google para la autenticación de usuarios. [...] Almacenamiento en la nube: Utiliza Amazon S3 para almacenar y recuperar archivos. [...] Procesamiento de pagos: Integra con Stripe para manejar pagos y suscripciones. [...] Análisis: Implementa Google Analytics para rastrear y analizar el tráfico del sitio. [...] Monitoreo de errores: Utiliza Sentry para rastrear y gestionar errores en la aplicación. [...] Correo Electrónico: Se conecta a Brevo para crear, enviar y programar correos electrónicos.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -706,34 +702,34 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>AU_04, AU_06</t>
+          <t>AU_04, AU_09, AU_11, AU_13, AU_15, AU_17, AU_19</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>system service, data service</t>
+          <t>system service, google, amazon s3, stripe, google analytics, sentry, brevo</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>CF_M08_AU24</t>
+          <t>CF_M08_AU25</t>
         </is>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
-          <t>• It communicates with the PostgreSQL database service</t>
+          <t>• Interacts with various external services for specific functionalities [...] Authentication</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0.8608</v>
+        <v>0.7479</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AU_29</t>
+          <t>AU_27</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -744,7 +740,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Se comunica directamente con Prisma para gestionar las consultas de la base de datos.</t>
+          <t>Data Service (PostgreSQL) [...] Se comunica directamente con Prisma para gestionar las consultas de la base de datos.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -754,7 +750,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>AU_06, AU_25</t>
+          <t>AU_06, AU_21</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -775,13 +771,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0.7562</v>
+        <v>0.8547</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AU_30</t>
+          <t>AU_28</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -792,42 +788,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Al interactuar con un componente de cliente, este puede acceder al servidor mediante el uso de las server actions.</t>
+          <t>System Service (Next.js) [...] Se comunica con el servicio de base de datos PostgreSQL (Data Service) utilizando Prisma como ORM.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>42</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>AU_04, AU_04</t>
+          <t>AU_04, AU_21</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>system service, system service</t>
+          <t>system service, prisma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
-          <t>CF_M08_P06</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>Client-Server</t>
-        </is>
-      </c>
+          <t>CF_M08_AU24</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
-          <t xml:space="preserve"> The Revivack application mainly uses Next.js for system development, which allows to separate the components between client and server rendering</t>
+          <t>• It communicates with the PostgreSQL database service</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0.8107</v>
+        <v>0.8399</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/evaluation/architecture/CF_M08_arch_eval_llm_report.xlsx
+++ b/outputs/evaluation/architecture/CF_M08_arch_eval_llm_report.xlsx
@@ -529,12 +529,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AU_23</t>
+          <t>AU_08</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>TypeScript</t>
+          <t>HTTP</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -544,96 +544,96 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cabe destacar que para desarrollar el sistema se ha empleado el lenguaje TypeScript.</t>
+          <t>Gestiona el enrutamiento de solicitudes HTTP y HTTPS hacia la aplicación Next.js.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>41</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>AU_04</t>
+          <t>AU_02</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
-          <t>CF_M08_AU05</t>
+          <t>CF_M08_AU23</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Next.js</t>
+          <t>HTTPS</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>System Service (Next.js)</t>
+          <t>HTTPS, which is the standard for secure communications on the web</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.894</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AU_24</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr"/>
+          <t>AU_25</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>TypeScript</t>
+        </is>
+      </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Connector</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Security Service (Traefik) [...] Gestiona el enrutamiento de solicitudes HTTP y HTTPS hacia la aplicación Next.js (System Service).</t>
+          <t>Cabe destacar que para desarrollar el sistema se ha empleado el lenguaje TypeScript.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>73</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>AU_02, AU_04</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>security service, system service</t>
-        </is>
-      </c>
+          <t>AU_04</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>CF_M08_AU23</t>
+          <t>CF_M08_AU05</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>HTTPS</t>
+          <t>Next.js</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>HTTPS, which is the standard for secure communications on the web</t>
+          <t>System Service (Next.js)</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0.7383</v>
+        <v>0.6879999999999999</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AU_25</t>
+          <t>AU_26</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -644,44 +644,48 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>System Service (Next.js) [...] Se comunica con el servicio de base de datos PostgreSQL (Data Service) utilizando Prisma como ORM.</t>
+          <t>Gestiona el enrutamiento de solicitudes HTTP y HTTPS hacia la aplicación Next.js (System Service).</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>41</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>AU_04, AU_06</t>
+          <t>AU_02, AU_04</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>system service, data service</t>
+          <t>security service, system service</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>CF_M08_AU24</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr"/>
+          <t>CF_M08_AU05</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Next.js</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>• It communicates with the PostgreSQL database service</t>
+          <t>System Service (Next.js)</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0.8399</v>
+        <v>0.7444</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AU_26</t>
+          <t>AU_27</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -692,7 +696,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>System Service (Next.js) [...] Interactúa con varios servicios externos para funcionalidades específicas: Autenticación: Utiliza Google para la autenticación de usuarios. [...] Almacenamiento en la nube: Utiliza Amazon S3 para almacenar y recuperar archivos. [...] Procesamiento de pagos: Integra con Stripe para manejar pagos y suscripciones. [...] Análisis: Implementa Google Analytics para rastrear y analizar el tráfico del sitio. [...] Monitoreo de errores: Utiliza Sentry para rastrear y gestionar errores en la aplicación. [...] Correo Electrónico: Se conecta a Brevo para crear, enviar y programar correos electrónicos.</t>
+          <t>Se comunica con el servicio de base de datos PostgreSQL (Data Service) utilizando Prisma como ORM.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -702,34 +706,34 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>AU_04, AU_09, AU_11, AU_13, AU_15, AU_17, AU_19</t>
+          <t>AU_04, AU_06</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>system service, google, amazon s3, stripe, google analytics, sentry, brevo</t>
+          <t>system service, data service</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>CF_M08_AU25</t>
+          <t>CF_M08_AU24</t>
         </is>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
-          <t>• Interacts with various external services for specific functionalities [...] Authentication</t>
+          <t>• It communicates with the PostgreSQL database service</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0.7479</v>
+        <v>0.8608</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AU_27</t>
+          <t>AU_28</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -740,7 +744,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Data Service (PostgreSQL) [...] Se comunica directamente con Prisma para gestionar las consultas de la base de datos.</t>
+          <t>Depende de Traefik para recibir y gestionar el tráfico HTTP/HTTPS.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -750,34 +754,38 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>AU_06, AU_21</t>
+          <t>AU_04, AU_02</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>data service, prisma</t>
+          <t>system service, security service</t>
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>CF_M08_AU24</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr"/>
+          <t>CF_M08_AU03</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Traefik</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>• It communicates with the PostgreSQL database service</t>
+          <t>Security Service (Traefik)</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0.8547</v>
+        <v>0.8131</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AU_28</t>
+          <t>AU_30</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -788,7 +796,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>System Service (Next.js) [...] Se comunica con el servicio de base de datos PostgreSQL (Data Service) utilizando Prisma como ORM.</t>
+          <t>Se comunica directamente con Prisma para gestionar las consultas de la base de datos.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -798,12 +806,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>AU_04, AU_21</t>
+          <t>AU_06, AU_10</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>system service, prisma</t>
+          <t>data service, prisma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
@@ -819,7 +827,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0.8399</v>
+        <v>0.7562</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/evaluation/architecture/CF_M08_arch_eval_llm_report.xlsx
+++ b/outputs/evaluation/architecture/CF_M08_arch_eval_llm_report.xlsx
@@ -529,7 +529,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AU_08</t>
+          <t>AU_20</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -544,17 +544,17 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Gestiona el enrutamiento de solicitudes HTTP y HTTPS hacia la aplicación Next.js.</t>
+          <t>Traefik abre el puerto 80 para manejar tráfico HTTP no seguro.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>43</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>AU_02</t>
+          <t>AU_03</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
@@ -644,7 +644,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Gestiona el enrutamiento de solicitudes HTTP y HTTPS hacia la aplicación Next.js (System Service).</t>
+          <t>Traefik gestiona el enrutamiento de solicitudes HTTP y HTTPS hacia la aplicación Next.js (System Service).</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -665,21 +665,21 @@
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>CF_M08_AU05</t>
+          <t>CF_M08_AU03</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Next.js</t>
+          <t>Traefik</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>System Service (Next.js)</t>
+          <t>Security Service (Traefik)</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0.7444</v>
+        <v>0.7524</v>
       </c>
     </row>
     <row r="6">
@@ -696,7 +696,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Se comunica con el servicio de base de datos PostgreSQL (Data Service) utilizando Prisma como ORM.</t>
+          <t>System Service (Next.js) se comunica con el servicio de base de datos PostgreSQL (Data Service) utilizando Prisma como ORM.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -727,13 +727,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0.8608</v>
+        <v>0.8296</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AU_28</t>
+          <t>AU_29</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -744,7 +744,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Depende de Traefik para recibir y gestionar el tráfico HTTP/HTTPS.</t>
+          <t>Data Service (PostgreSQL) se comunica directamente con Prisma para gestionar las consultas de la base de datos.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -754,32 +754,28 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>AU_04, AU_02</t>
+          <t>AU_06, AU_23</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>system service, security service</t>
+          <t>data service, prisma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>CF_M08_AU03</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>Traefik</t>
-        </is>
-      </c>
+          <t>CF_M08_AU24</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Security Service (Traefik)</t>
+          <t>• It communicates with the PostgreSQL database service</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0.8131</v>
+        <v>0.8529</v>
       </c>
     </row>
     <row r="8">
@@ -796,38 +792,42 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Se comunica directamente con Prisma para gestionar las consultas de la base de datos.</t>
+          <t>Traefik abre el puerto 80 para manejar tráfico HTTP no seguro [...] Traefik abre el puerto 443 para manejar tráfico HTTPS.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>43</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>AU_06, AU_10</t>
+          <t>AU_02, AU_20, AU_21</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>data service, prisma</t>
+          <t>security service, http, https</t>
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
-          <t>CF_M08_AU24</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr"/>
+          <t>CF_M08_AU23</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>HTTPS</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>• It communicates with the PostgreSQL database service</t>
+          <t>HTTPS, which is the standard for secure communications on the web</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0.7562</v>
+        <v>0.756</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/evaluation/architecture/CF_M08_arch_eval_llm_report.xlsx
+++ b/outputs/evaluation/architecture/CF_M08_arch_eval_llm_report.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L8"/>
+  <dimension ref="A1:L12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -454,7 +454,7 @@
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>LLM_fixes</t>
+          <t>LLM_fixedType</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
@@ -529,7 +529,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AU_20</t>
+          <t>AU_22</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -544,7 +544,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Traefik abre el puerto 80 para manejar tráfico HTTP no seguro.</t>
+          <t>Traefik abre el puerto 80 para manejar tráfico HTTP.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -554,7 +554,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>AU_03</t>
+          <t>AU_02, AU_26</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
@@ -581,7 +581,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AU_25</t>
+          <t>AU_24</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -733,7 +733,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AU_29</t>
+          <t>AU_28</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -744,7 +744,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Data Service (PostgreSQL) se comunica directamente con Prisma para gestionar las consultas de la base de datos.</t>
+          <t>System Service (Next.js) utiliza Google para la autenticación de usuarios.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -754,34 +754,38 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>AU_06, AU_23</t>
+          <t>AU_04, AU_10</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>data service, prisma</t>
+          <t>system service, authentication service</t>
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>CF_M08_AU24</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr"/>
+          <t>CF_M08_AU05</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Next.js</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>• It communicates with the PostgreSQL database service</t>
+          <t>System Service (Next.js)</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0.8529</v>
+        <v>0.7514</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AU_30</t>
+          <t>AU_29</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -792,42 +796,250 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Traefik abre el puerto 80 para manejar tráfico HTTP no seguro [...] Traefik abre el puerto 443 para manejar tráfico HTTPS.</t>
+          <t>System Service (Next.js) utiliza Amazon S3 para almacenar y recuperar archivos.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>42</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>AU_02, AU_20, AU_21</t>
+          <t>AU_04, AU_12</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>security service, http, https</t>
+          <t>system service, cloud storage service</t>
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
-          <t>CF_M08_AU23</t>
+          <t>CF_M08_AU13</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>HTTPS</t>
+          <t>Amazon S3</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>HTTPS, which is the standard for secure communications on the web</t>
+          <t>Cloud storage: Use Amazon S3 to store and retrieve files.</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0.756</v>
+        <v>0.7913</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>AU_30</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>System Service (Next.js) integra con Stripe para manejar pagos y suscripciones.</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>AU_04, AU_14</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>system service, payment processing service</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>CF_M08_AU05</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Next.js</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>System Service (Next.js)</t>
+        </is>
+      </c>
+      <c r="L9" t="n">
+        <v>0.7436</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>AU_31</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>System Service (Next.js) implementa Google Analytics para rastrear y analizar el tráfico del sitio.</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>AU_04, AU_16</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>system service, analytics service</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>CF_M08_AU17</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Google Analytics</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Implement Google Analytics to track and analyze site traffic</t>
+        </is>
+      </c>
+      <c r="L10" t="n">
+        <v>0.7814</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>AU_32</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>System Service (Next.js) utiliza Sentry para rastrear y gestionar errores en la aplicación.</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>AU_04, AU_18</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>system service, error monitoring service</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>CF_M08_AU05</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Next.js</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>System Service (Next.js)</t>
+        </is>
+      </c>
+      <c r="L11" t="n">
+        <v>0.7448</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>AU_33</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>System Service (Next.js) se conecta a Brevo para crear, enviar y programar correos electrónicos.</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>AU_04, AU_20</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>system service, email service</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>CF_M08_AU05</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Next.js</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>System Service (Next.js)</t>
+        </is>
+      </c>
+      <c r="L12" t="n">
+        <v>0.7239</v>
       </c>
     </row>
   </sheetData>
